--- a/ru/downloads/data-excel/17.8.1.xlsx
+++ b/ru/downloads/data-excel/17.8.1.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\korozbaeva\Desktop\Показатели ЦУР для Платформы\Глобальные показатели ЦУР\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\Показатели ЦУР для Платформы\Глобальные показатели ЦУР — 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14175" windowHeight="8070"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12135"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -945,7 +945,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:J50"/>
   <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="3" width="36.7109375" style="14" customWidth="1"/>
@@ -954,7 +954,7 @@
     <col min="10" max="16384" width="9.140625" style="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="43" t="s">
         <v>15</v>
       </c>
@@ -965,7 +965,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="7" t="s">
         <v>3</v>
       </c>
@@ -977,14 +977,15 @@
       </c>
       <c r="D2" s="30"/>
     </row>
-    <row r="3" spans="1:9" ht="12.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3"/>
       <c r="B3" s="4"/>
       <c r="C3" s="5"/>
       <c r="D3" s="30"/>
       <c r="E3" s="30"/>
-    </row>
-    <row r="4" spans="1:9" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="J3"/>
+    </row>
+    <row r="4" spans="1:10" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>0</v>
       </c>
@@ -1012,8 +1013,11 @@
       <c r="I4" s="41">
         <v>2023</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" s="29" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J4" s="41">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" s="29" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
         <v>23</v>
       </c>
@@ -1041,8 +1045,11 @@
       <c r="I5" s="36">
         <v>86.113021088083215</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J5" s="29">
+        <v>86.4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="22" t="s">
         <v>25</v>
       </c>
@@ -1058,7 +1065,7 @@
       <c r="H6" s="16"/>
       <c r="I6" s="16"/>
     </row>
-    <row r="7" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="31" t="s">
         <v>27</v>
       </c>
@@ -1086,8 +1093,11 @@
       <c r="I7" s="16">
         <v>90.052395231935563</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J7" s="14">
+        <v>87.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="31" t="s">
         <v>29</v>
       </c>
@@ -1115,8 +1125,11 @@
       <c r="I8" s="16">
         <v>83.650064565805053</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J8" s="14">
+        <v>85.6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="22" t="s">
         <v>95</v>
       </c>
@@ -1132,7 +1145,7 @@
       <c r="H9" s="16"/>
       <c r="I9" s="16"/>
     </row>
-    <row r="10" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="23" t="s">
         <v>31</v>
       </c>
@@ -1160,8 +1173,11 @@
       <c r="I10" s="16">
         <v>86.825494089174455</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J10" s="14">
+        <v>86.8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="23" t="s">
         <v>33</v>
       </c>
@@ -1189,8 +1205,11 @@
       <c r="I11" s="16">
         <v>85.508401665267698</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J11" s="14">
+        <v>86.2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="45" t="s">
         <v>97</v>
       </c>
@@ -1206,7 +1225,7 @@
       <c r="H12" s="16"/>
       <c r="I12" s="16"/>
     </row>
-    <row r="13" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="23" t="s">
         <v>35</v>
       </c>
@@ -1234,8 +1253,11 @@
       <c r="I13" s="16">
         <v>83.431006248132036</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J13" s="14">
+        <v>84.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="23" t="s">
         <v>38</v>
       </c>
@@ -1263,8 +1285,11 @@
       <c r="I14" s="16">
         <v>69.978703396630792</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J14" s="14">
+        <v>74.599999999999994</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="23" t="s">
         <v>41</v>
       </c>
@@ -1292,8 +1317,11 @@
       <c r="I15" s="16">
         <v>89.438446897118652</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J15" s="14">
+        <v>88.3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="23" t="s">
         <v>44</v>
       </c>
@@ -1321,8 +1349,11 @@
       <c r="I16" s="16">
         <v>85.050448319380493</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J16" s="14">
+        <v>86.8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="24" t="s">
         <v>47</v>
       </c>
@@ -1350,8 +1381,11 @@
       <c r="I17" s="16">
         <v>90.731106591108357</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J17" s="14">
+        <v>89.6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="24" t="s">
         <v>50</v>
       </c>
@@ -1379,8 +1413,11 @@
       <c r="I18" s="16">
         <v>87.049095014451183</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J18" s="14">
+        <v>91.2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="14" t="s">
         <v>53</v>
       </c>
@@ -1408,8 +1445,11 @@
       <c r="I19" s="16">
         <v>88.380153048901903</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J19" s="14">
+        <v>89.8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="14" t="s">
         <v>56</v>
       </c>
@@ -1437,8 +1477,11 @@
       <c r="I20" s="16">
         <v>95.059232846432664</v>
       </c>
-    </row>
-    <row r="21" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J20" s="14">
+        <v>90.8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="14" t="s">
         <v>59</v>
       </c>
@@ -1466,8 +1509,11 @@
       <c r="I21" s="16">
         <v>90.384389589564591</v>
       </c>
-    </row>
-    <row r="22" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J21" s="14">
+        <v>88.9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="15" t="s">
         <v>99</v>
       </c>
@@ -1483,7 +1529,7 @@
       <c r="H22" s="16"/>
       <c r="I22" s="16"/>
     </row>
-    <row r="23" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="14" t="s">
         <v>62</v>
       </c>
@@ -1511,8 +1557,11 @@
       <c r="I23" s="16">
         <v>94.48054002633701</v>
       </c>
-    </row>
-    <row r="24" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J23" s="14">
+        <v>90.5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="14" t="s">
         <v>93</v>
       </c>
@@ -1540,8 +1589,11 @@
       <c r="I24" s="16">
         <v>90.371556857711852</v>
       </c>
-    </row>
-    <row r="25" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J24" s="14">
+        <v>89.8</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="14" t="s">
         <v>94</v>
       </c>
@@ -1569,8 +1621,11 @@
       <c r="I25" s="16">
         <v>62.580311693710286</v>
       </c>
-    </row>
-    <row r="26" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J25" s="14">
+        <v>72.2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="15" t="s">
         <v>101</v>
       </c>
@@ -1586,7 +1641,7 @@
       <c r="H26" s="16"/>
       <c r="I26" s="16"/>
     </row>
-    <row r="27" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="14" t="s">
         <v>67</v>
       </c>
@@ -1614,8 +1669,11 @@
       <c r="I27" s="16">
         <v>68.716149044597714</v>
       </c>
-    </row>
-    <row r="28" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J27" s="14">
+        <v>75.599999999999994</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="14" t="s">
         <v>69</v>
       </c>
@@ -1643,8 +1701,11 @@
       <c r="I28" s="16">
         <v>87.508827266167032</v>
       </c>
-    </row>
-    <row r="29" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J28" s="14">
+        <v>87.7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="14" t="s">
         <v>71</v>
       </c>
@@ -1672,8 +1733,11 @@
       <c r="I29" s="16">
         <v>81.939359306250495</v>
       </c>
-    </row>
-    <row r="30" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J29" s="14">
+        <v>83.1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="31" t="s">
         <v>73</v>
       </c>
@@ -1701,8 +1765,11 @@
       <c r="I30" s="37">
         <v>89.93259718493691</v>
       </c>
-    </row>
-    <row r="31" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J30" s="14">
+        <v>89.7</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="33" t="s">
         <v>76</v>
       </c>
@@ -1730,8 +1797,11 @@
       <c r="I31" s="16">
         <v>96.031269704782474</v>
       </c>
-    </row>
-    <row r="32" spans="1:9" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J31" s="14">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="22" t="s">
         <v>78</v>
       </c>
@@ -1748,7 +1818,7 @@
       <c r="H32" s="16"/>
       <c r="I32" s="16"/>
     </row>
-    <row r="33" spans="1:9" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="31" t="s">
         <v>80</v>
       </c>
@@ -1776,8 +1846,11 @@
       <c r="I33" s="16">
         <v>85.840483399183398</v>
       </c>
-    </row>
-    <row r="34" spans="1:9" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J33" s="14">
+        <v>87.7</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="31" t="s">
         <v>82</v>
       </c>
@@ -1805,8 +1878,11 @@
       <c r="I34" s="16">
         <v>85.612866567454745</v>
       </c>
-    </row>
-    <row r="35" spans="1:9" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J34" s="14">
+        <v>85.8</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="31" t="s">
         <v>84</v>
       </c>
@@ -1834,8 +1910,11 @@
       <c r="I35" s="16">
         <v>84.73325342138196</v>
       </c>
-    </row>
-    <row r="36" spans="1:9" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J35" s="14">
+        <v>87.4</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="31" t="s">
         <v>86</v>
       </c>
@@ -1863,8 +1942,11 @@
       <c r="I36" s="16">
         <v>85.232733591272591</v>
       </c>
-    </row>
-    <row r="37" spans="1:9" customFormat="1" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J36" s="14">
+        <v>85.3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" customFormat="1" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="32" t="s">
         <v>88</v>
       </c>
@@ -1892,8 +1974,11 @@
       <c r="I37" s="35">
         <v>88.581026729085679</v>
       </c>
-    </row>
-    <row r="38" spans="1:9" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J37" s="35">
+        <v>86.3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="44" t="s">
         <v>90</v>
       </c>
@@ -1904,48 +1989,48 @@
         <v>92</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A39" s="31"/>
       <c r="C39" s="17"/>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A40" s="31"/>
       <c r="C40" s="17"/>
       <c r="D40" s="16"/>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A41" s="26"/>
       <c r="B41" s="15"/>
       <c r="C41" s="19"/>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A42" s="31"/>
       <c r="C42" s="20"/>
       <c r="D42" s="16"/>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A43" s="31"/>
       <c r="C43" s="20"/>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A44" s="19"/>
       <c r="B44" s="15"/>
       <c r="C44" s="19"/>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A45" s="25"/>
       <c r="C45" s="17"/>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A46" s="25"/>
       <c r="C46" s="17"/>
       <c r="D46" s="16"/>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A47" s="25"/>
       <c r="C47" s="17"/>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A48" s="27"/>
       <c r="B48" s="13"/>
       <c r="C48" s="17"/>
